--- a/resources/Part_3_Statistics/S20_L128/4.6.Test-for-the-mean.Population-variance-unknown-exercise.xlsx
+++ b/resources/Part_3_Statistics/S20_L128/4.6.Test-for-the-mean.Population-variance-unknown-exercise.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="18326"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Iliya\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\D\GitRepos\StatisticsBAandDS\DataScienceBootcamp\resources\Part_3_Statistics\S20_L128\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19272" windowHeight="7620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19275" windowHeight="7620"/>
   </bookViews>
   <sheets>
     <sheet name="Open rate dataset" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="31">
   <si>
     <t>p-value</t>
   </si>
@@ -132,11 +132,23 @@
   <si>
     <t>One-sided</t>
   </si>
+  <si>
+    <t>At 5% significance there is no enough evidence to reject that the open rate is 40%.</t>
+  </si>
+  <si>
+    <t>At 1% significance there is no enough evidence to reject that the open rate is 40%.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two-sided P-value: </t>
+  </si>
+  <si>
+    <t>since 0,608&gt;0,05 and 0,608&gt;0,01, we cannot reject that the open rate is 40%</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
@@ -230,7 +242,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -250,10 +262,11 @@
     <xf numFmtId="164" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -564,38 +577,38 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:M41"/>
-  <sheetFormatPr defaultRowHeight="11.4" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10.6640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.44140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.5546875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="11.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="8.88671875" style="1"/>
-    <col min="11" max="11" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="8.88671875" style="1"/>
+    <col min="2" max="2" width="10.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.42578125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.5703125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="8.85546875" style="1"/>
+    <col min="11" max="11" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B1" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="2:13" ht="12" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="2:13" ht="12" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B3" s="2"/>
     </row>
-    <row r="4" spans="2:13" ht="12" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B4" s="2" t="s">
         <v>12</v>
       </c>
@@ -603,7 +616,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="2:13" ht="12" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
         <v>14</v>
       </c>
@@ -611,7 +624,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="2:13" ht="12" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B6" s="2"/>
       <c r="C6" s="2" t="s">
         <v>16</v>
@@ -620,7 +633,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="2:13" ht="12" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B7" s="2"/>
       <c r="C7" s="2" t="s">
         <v>17</v>
@@ -629,7 +642,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="2:13" ht="12" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B8" s="2"/>
       <c r="C8" s="2" t="s">
         <v>18</v>
@@ -638,12 +651,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="2:13" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:13" ht="12.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B10" s="7" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="2:13" ht="12" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B11" s="5">
         <v>0.26</v>
       </c>
@@ -659,7 +672,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="2:13" ht="12" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B12" s="5">
         <v>0.23</v>
       </c>
@@ -672,7 +685,7 @@
         <v>0.13736002976767953</v>
       </c>
     </row>
-    <row r="13" spans="2:13" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:13" ht="12.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B13" s="5">
         <v>0.42</v>
       </c>
@@ -698,7 +711,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="2:13" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="B14" s="5">
         <v>0.49</v>
       </c>
@@ -712,9 +725,19 @@
       <c r="I14" s="1">
         <v>1.83</v>
       </c>
+      <c r="J14" s="1">
+        <v>2.262</v>
+      </c>
+      <c r="K14" s="1" t="b">
+        <f>J14&lt;ABS($E$16)</f>
+        <v>0</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="M14" s="9"/>
     </row>
-    <row r="15" spans="2:13" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:13" ht="13.5" x14ac:dyDescent="0.25">
       <c r="B15" s="5">
         <v>0.23</v>
       </c>
@@ -734,8 +757,18 @@
       <c r="I15" s="1">
         <v>2.82</v>
       </c>
-    </row>
-    <row r="16" spans="2:13" ht="12" x14ac:dyDescent="0.25">
+      <c r="J15" s="1">
+        <v>3.25</v>
+      </c>
+      <c r="K15" s="1" t="b">
+        <f>J15&lt;ABS($E$16)</f>
+        <v>0</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B16" s="5">
         <v>0.59</v>
       </c>
@@ -754,7 +787,10 @@
       <c r="I16" s="4">
         <v>0.30399999999999999</v>
       </c>
-      <c r="J16" s="12"/>
+      <c r="J16" s="12">
+        <f>I16*2</f>
+        <v>0.60799999999999998</v>
+      </c>
       <c r="K16" s="12" t="s">
         <v>20</v>
       </c>
@@ -762,13 +798,13 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B17" s="5">
         <v>0.28999999999999998</v>
       </c>
       <c r="C17" s="13"/>
     </row>
-    <row r="18" spans="2:10" ht="12" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B18" s="5">
         <v>0.28999999999999998</v>
       </c>
@@ -776,20 +812,31 @@
       <c r="G18" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H18" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J18" s="15">
+        <f>J16</f>
+        <v>0.60799999999999998</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="5">
         <v>0.56999999999999995</v>
       </c>
       <c r="C19" s="13"/>
-    </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H19" s="2"/>
+    </row>
+    <row r="20" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B20" s="6">
         <v>0.4</v>
       </c>
       <c r="C20" s="13"/>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J32" s="14"/>
     </row>
     <row r="33" spans="10:10" x14ac:dyDescent="0.2">
